--- a/03_Procurement_Supply_Stock_Alert.xlsx
+++ b/03_Procurement_Supply_Stock_Alert.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N3"/>
+  <dimension ref="A1:AA4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -439,14 +439,14 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
+          <t>Quantity Required</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
           <t>Quantity Available</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Quantity Required</t>
-        </is>
-      </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>Shortage Quantity</t>
@@ -454,44 +454,109 @@
       </c>
       <c r="H1" t="inlineStr">
         <is>
+          <t>Stock Status</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>Warehouse Notification</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>Daily Consumption</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>Lead Time</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Safety Stock</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Reorder Point</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Reorder Status</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
+        <is>
+          <t>Estimated Stock-Out Date</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
           <t>Last Updated</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>Production Line</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Warehouse Location</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Comments</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
         <is>
           <t>Supplier</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Purchase Order</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
+      <c r="V1" t="inlineStr">
         <is>
           <t>Order Date</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>ETA</t>
-        </is>
-      </c>
-      <c r="M1" t="inlineStr">
-        <is>
-          <t>Purchasing Status</t>
-        </is>
-      </c>
-      <c r="N1" t="inlineStr">
-        <is>
-          <t>Comments</t>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>Expected Delivery Date</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PO Number</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>Transport</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>Truck Number</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>Transport Status</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALT-001</t>
+          <t>ALT-002</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -501,76 +566,255 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TEST-001</t>
+          <t>TEST-002</t>
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
       <c r="E2" t="n">
+        <v>500</v>
+      </c>
+      <c r="F2" t="n">
+        <v>400</v>
+      </c>
+      <c r="G2" t="n">
         <v>100</v>
       </c>
-      <c r="F2" t="n">
-        <v>100</v>
-      </c>
-      <c r="G2" t="n">
-        <v>0</v>
-      </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr"/>
+          <t>🔴 Shortage</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>🚨 Critical</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>🚨 ALERT: 🔴 Shortage (Shortage: 100 units)</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>7</v>
+      </c>
+      <c r="L2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M2" t="n">
+        <v>10</v>
+      </c>
+      <c r="N2" t="n">
+        <v>45</v>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>No Reorder Required</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2026-11-19</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:42</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
+      <c r="U2" t="inlineStr">
+        <is>
+          <t>Default Supplier</t>
+        </is>
+      </c>
+      <c r="V2" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="W2" t="inlineStr">
+        <is>
+          <t>2026-09-30</t>
+        </is>
+      </c>
+      <c r="X2" t="inlineStr">
+        <is>
+          <t>PO-TEST-002</t>
+        </is>
+      </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>Road</t>
+        </is>
+      </c>
+      <c r="Z2" t="inlineStr"/>
+      <c r="AA2" t="inlineStr">
+        <is>
+          <t>In Transit</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALT-002</t>
+          <t>ALT-ALT-005</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>TEST-002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr"/>
+          <t>ALT-005</t>
+        </is>
+      </c>
+      <c r="D3" t="n">
+        <v>0</v>
+      </c>
       <c r="E3" t="n">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="F3" t="n">
-        <v>500</v>
+        <v>1</v>
       </c>
       <c r="G3" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2026-09-21 17:05</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>Pending</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr"/>
+          <t>🔴 Shortage</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>🚨 Critical</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>🚨 ALERT: 🔴 Shortage (Shortage: 99 units)</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>5</v>
+      </c>
+      <c r="L3" t="n">
+        <v>5</v>
+      </c>
+      <c r="M3" t="n">
+        <v>10</v>
+      </c>
+      <c r="N3" t="n">
+        <v>35</v>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>Reorder Triggered</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:42</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ALT-TEST-004</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2026-09-23</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>TEST-004</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="n">
+        <v>10</v>
+      </c>
+      <c r="F4" t="n">
+        <v>11</v>
+      </c>
+      <c r="G4" t="n">
+        <v>0</v>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>🟠 Low Stock</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>🟠 Medium</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>⚠️ WARNING: Low Stock Level</t>
+        </is>
+      </c>
+      <c r="K4" t="n">
+        <v>5</v>
+      </c>
+      <c r="L4" t="n">
+        <v>5</v>
+      </c>
+      <c r="M4" t="n">
+        <v>10</v>
+      </c>
+      <c r="N4" t="n">
+        <v>35</v>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>Reorder Triggered</t>
+        </is>
+      </c>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>2026-09-25</t>
+        </is>
+      </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>2026-09-23 16:42</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr"/>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/03_Procurement_Supply_Stock_Alert.xlsx
+++ b/03_Procurement_Supply_Stock_Alert.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:42</t>
+          <t>2026-09-23 16:43</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:42</t>
+          <t>2026-09-23 16:43</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-23 16:42</t>
+          <t>2026-09-23 16:43</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>

--- a/03_Procurement_Supply_Stock_Alert.xlsx
+++ b/03_Procurement_Supply_Stock_Alert.xlsx
@@ -618,7 +618,7 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:43</t>
+          <t>2026-09-23 16:44</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
@@ -723,7 +723,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:43</t>
+          <t>2026-09-23 16:44</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -802,7 +802,7 @@
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>2026-09-23 16:43</t>
+          <t>2026-09-23 16:44</t>
         </is>
       </c>
       <c r="R4" t="inlineStr"/>

--- a/03_Procurement_Supply_Stock_Alert.xlsx
+++ b/03_Procurement_Supply_Stock_Alert.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AA4"/>
+  <dimension ref="A1:AA3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -556,28 +556,30 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>ALT-002</t>
+          <t>ALT-ALT-005</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>TEST-002</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr"/>
+          <t>ALT-005</t>
+        </is>
+      </c>
+      <c r="D2" t="n">
+        <v>0</v>
+      </c>
       <c r="E2" t="n">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="F2" t="n">
-        <v>400</v>
+        <v>1</v>
       </c>
       <c r="G2" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
@@ -591,11 +593,11 @@
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>🚨 ALERT: 🔴 Shortage (Shortage: 100 units)</t>
+          <t>🚨 ALERT: 🔴 Shortage (Shortage: 99 units)</t>
         </is>
       </c>
       <c r="K2" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L2" t="n">
         <v>5</v>
@@ -604,62 +606,38 @@
         <v>10</v>
       </c>
       <c r="N2" t="n">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>No Reorder Required</t>
+          <t>Reorder Triggered</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>2026-11-19</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44</t>
+          <t>2026-09-23 16:53</t>
         </is>
       </c>
       <c r="R2" t="inlineStr"/>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>Default Supplier</t>
-        </is>
-      </c>
-      <c r="V2" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="W2" t="inlineStr">
-        <is>
-          <t>2026-09-30</t>
-        </is>
-      </c>
-      <c r="X2" t="inlineStr">
-        <is>
-          <t>PO-TEST-002</t>
-        </is>
-      </c>
-      <c r="Y2" t="inlineStr">
-        <is>
-          <t>Road</t>
-        </is>
-      </c>
+      <c r="U2" t="inlineStr"/>
+      <c r="V2" t="inlineStr"/>
+      <c r="W2" t="inlineStr"/>
+      <c r="X2" t="inlineStr"/>
+      <c r="Y2" t="inlineStr"/>
       <c r="Z2" t="inlineStr"/>
-      <c r="AA2" t="inlineStr">
-        <is>
-          <t>In Transit</t>
-        </is>
-      </c>
+      <c r="AA2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ALT-ALT-005</t>
+          <t>ALT-TEST-004</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -669,34 +647,32 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>ALT-005</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+          <t>TEST-004</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="n">
+        <v>10</v>
+      </c>
+      <c r="F3" t="n">
+        <v>11</v>
+      </c>
+      <c r="G3" t="n">
         <v>0</v>
       </c>
-      <c r="E3" t="n">
-        <v>100</v>
-      </c>
-      <c r="F3" t="n">
-        <v>1</v>
-      </c>
-      <c r="G3" t="n">
-        <v>99</v>
-      </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>🔴 Shortage</t>
+          <t>🟠 Low Stock</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>🚨 Critical</t>
+          <t>🟠 Medium</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>🚨 ALERT: 🔴 Shortage (Shortage: 99 units)</t>
+          <t>⚠️ WARNING: Low Stock Level</t>
         </is>
       </c>
       <c r="K3" t="n">
@@ -718,12 +694,12 @@
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>2026-09-23</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:44</t>
+          <t>2026-09-23 16:53</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
@@ -737,85 +713,6 @@
       <c r="Z3" t="inlineStr"/>
       <c r="AA3" t="inlineStr"/>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ALT-TEST-004</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2026-09-23</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>TEST-004</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="n">
-        <v>10</v>
-      </c>
-      <c r="F4" t="n">
-        <v>11</v>
-      </c>
-      <c r="G4" t="n">
-        <v>0</v>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>🟠 Low Stock</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>🟠 Medium</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>⚠️ WARNING: Low Stock Level</t>
-        </is>
-      </c>
-      <c r="K4" t="n">
-        <v>5</v>
-      </c>
-      <c r="L4" t="n">
-        <v>5</v>
-      </c>
-      <c r="M4" t="n">
-        <v>10</v>
-      </c>
-      <c r="N4" t="n">
-        <v>35</v>
-      </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>Reorder Triggered</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2026-09-25</t>
-        </is>
-      </c>
-      <c r="Q4" t="inlineStr">
-        <is>
-          <t>2026-09-23 16:44</t>
-        </is>
-      </c>
-      <c r="R4" t="inlineStr"/>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/03_Procurement_Supply_Stock_Alert.xlsx
+++ b/03_Procurement_Supply_Stock_Alert.xlsx
@@ -620,10 +620,14 @@
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>2026-09-23 16:53</t>
-        </is>
-      </c>
-      <c r="R2" t="inlineStr"/>
+          <t>2026-09-23 16:54</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>Line-A</t>
+        </is>
+      </c>
       <c r="S2" t="inlineStr"/>
       <c r="T2" t="inlineStr"/>
       <c r="U2" t="inlineStr"/>
@@ -699,7 +703,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>2026-09-23 16:53</t>
+          <t>2026-09-23 16:54</t>
         </is>
       </c>
       <c r="R3" t="inlineStr"/>
